--- a/reports/web-export-quarterly-reports/web-export-starting-file-South-Maui.xlsx
+++ b/reports/web-export-quarterly-reports/web-export-starting-file-South-Maui.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10802"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bill/development/water-quality/hui-reports/reports/web-export-quarterly-reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dan/hui/hui-reports/reports/web-export-quarterly-reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F22983F-4F16-1C4B-83AD-BAE2CAA65411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6128BF2-FC9E-BA41-A4F7-3EBC75468B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20060" yWindow="2700" windowWidth="32160" windowHeight="22420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta data" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="130407" concurrentCalc="0"/>
+  <calcPr calcId="130407"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -154,9 +154,6 @@
     <t>Time</t>
   </si>
   <si>
-    <t>Falinski, Kim, Reed, Dana, Callender, Tova, Fielding, Emily, Newbold, Robin, &amp; Yurkanin, Alana. (2017). Hui o ka Wai Ola Water Quality Data [Data set]. Zenodo. http://doi.org/10.5281/zenodo.830049</t>
-  </si>
-  <si>
     <t>APHA Method 4500-P, GF/F-filtered grab samples, SEAL Analytical AA3 autoanalyzer</t>
   </si>
   <si>
@@ -197,6 +194,9 @@
   </si>
   <si>
     <t>Ammonium-OPA Method, GF/F-filtered grab samples, SEAL Analytical AA3 autoanalyzer</t>
+  </si>
+  <si>
+    <t>Hui O Ka Wai Ola Water Quality Data. https://www.huiokawaiola.com/data.html</t>
   </si>
 </sst>
 </file>
@@ -248,7 +248,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -260,9 +260,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -641,12 +638,12 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -669,20 +666,20 @@
     </row>
     <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -692,17 +689,17 @@
         <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -822,7 +819,7 @@
         <v>33</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="32" x14ac:dyDescent="0.2">
@@ -836,7 +833,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="32" x14ac:dyDescent="0.2">
@@ -850,7 +847,7 @@
         <v>33</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="32" x14ac:dyDescent="0.2">
@@ -864,7 +861,7 @@
         <v>33</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="32" x14ac:dyDescent="0.2">
@@ -878,7 +875,7 @@
         <v>33</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -886,13 +883,13 @@
         <v>11</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.2">
@@ -903,7 +900,7 @@
     </row>
     <row r="26" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="4"/>
@@ -911,9 +908,9 @@
     </row>
     <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="e">
